--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -724,7 +724,7 @@
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 constr-bind-type:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
  TRE_A05-TypeDocComplementaireCISIS, OID : 1.2.250.1.213.1.1.4.12
- TRE_A04-TypeDocument-LOINC, OID : 2.16.840.1.113883.6.1
+ LOINC, OID : 2.16.840.1.113883.6.1
  TRE_A12-NomenclatureASTM, OID : ASTM
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J66-TypeCode-DMP).
 En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J07-XdsTypeCode-CISIS peut être utilisé. {null}</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1320">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -786,7 +786,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -802,11 +802,11 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif. Pour les documents d’expression personnelle du patient, cet attribut fait référence au patient.</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>
@@ -3866,13 +3866,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
-</t>
-  </si>
-  <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
-  </si>
-  <si>
     <t>Relationships to other documents</t>
   </si>
   <si>
@@ -4032,10 +4025,6 @@
     <t>List.extension:PDSmintendedRecipient.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.SubmissionSetUniqueIdIdentifier}
 </t>
   </si>
@@ -4067,6 +4056,10 @@
   </si>
   <si>
     <t>Représente la date et heure de soumission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
+</t>
   </si>
   <si>
     <t>Représente l'auteur du lot de soumission. Si l'auteur est une organisation, utiliser l'extension authorOrg. Si l’auteur est une personne physique ou un dispositif, utiliser l’attribut source.reference .</t>
@@ -5619,7 +5612,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="174">
@@ -5627,7 +5620,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="175">
@@ -5643,7 +5636,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="177">
@@ -5651,7 +5644,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="178">
@@ -5705,7 +5698,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="185">
@@ -5749,7 +5742,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="191">
@@ -8864,7 +8857,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -73710,10 +73703,10 @@
         <v>75</v>
       </c>
       <c r="L651" t="s" s="2">
-        <v>1235</v>
+        <v>1001</v>
       </c>
       <c r="M651" t="s" s="2">
-        <v>1236</v>
+        <v>249</v>
       </c>
       <c r="N651" t="s" s="2">
         <v>250</v>
@@ -73923,10 +73916,10 @@
         <v>258</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>261</v>
@@ -74343,7 +74336,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>273</v>
@@ -74448,7 +74441,7 @@
         <v>278</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>280</v>
@@ -74765,7 +74758,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75704,7 +75697,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75811,7 +75804,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76237,7 +76230,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77240,7 +77233,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="685">
@@ -77345,7 +77338,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="686">
@@ -77558,7 +77551,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77661,7 +77654,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77766,7 +77759,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77869,7 +77862,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77972,7 +77965,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78077,7 +78070,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78182,7 +78175,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78287,7 +78280,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78392,7 +78385,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78497,7 +78490,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78602,7 +78595,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78707,7 +78700,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78812,7 +78805,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78917,7 +78910,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79022,7 +79015,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79054,7 +79047,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79127,7 +79120,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79141,7 +79134,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79228,7 +79221,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79262,7 +79255,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79328,18 +79321,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79436,13 +79429,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79539,13 +79532,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79585,7 +79578,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79644,13 +79637,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79710,7 +79703,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79745,16 +79738,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79776,13 +79769,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
+        <v>1266</v>
+      </c>
+      <c r="M709" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="N709" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="M709" t="s" s="2">
-        <v>1269</v>
-      </c>
-      <c r="N709" t="s" s="2">
-        <v>1270</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79850,16 +79843,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79881,13 +79874,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="M710" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="N710" t="s" s="2">
         <v>1273</v>
-      </c>
-      <c r="M710" t="s" s="2">
-        <v>1274</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79955,10 +79948,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -79989,7 +79982,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80060,16 +80053,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80091,10 +80084,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80165,13 +80158,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80268,13 +80261,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80371,13 +80364,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80476,13 +80469,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80505,7 +80498,7 @@
         <v>75</v>
       </c>
       <c r="L716" t="s" s="2">
-        <v>1286</v>
+        <v>248</v>
       </c>
       <c r="M716" t="s" s="2">
         <v>1002</v>
@@ -80579,7 +80572,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80682,7 +80675,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80783,7 +80776,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80814,10 +80807,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80888,7 +80881,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80922,7 +80915,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -80993,7 +80986,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81025,7 +81018,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81098,7 +81091,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81130,7 +81123,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81205,7 +81198,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81237,7 +81230,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81310,7 +81303,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81342,7 +81335,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81361,7 +81354,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81415,7 +81408,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81522,7 +81515,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81625,7 +81618,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81657,7 +81650,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81732,7 +81725,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81761,10 +81754,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>243</v>
+        <v>1293</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81839,13 +81832,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81942,13 +81935,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82047,16 +82040,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C731" t="s" s="2">
+        <v>1296</v>
+      </c>
+      <c r="D731" t="s" s="2">
         <v>1298</v>
-      </c>
-      <c r="D731" t="s" s="2">
-        <v>1300</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82078,13 +82071,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
+        <v>1299</v>
+      </c>
+      <c r="M731" t="s" s="2">
+        <v>1300</v>
+      </c>
+      <c r="N731" t="s" s="2">
         <v>1301</v>
-      </c>
-      <c r="M731" t="s" s="2">
-        <v>1302</v>
-      </c>
-      <c r="N731" t="s" s="2">
-        <v>1303</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82152,13 +82145,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82255,13 +82248,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82358,13 +82351,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82404,7 +82397,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82463,13 +82456,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82492,7 +82485,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82566,13 +82559,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82671,13 +82664,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82776,13 +82769,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82881,13 +82874,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82986,7 +82979,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83093,7 +83086,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83125,7 +83118,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83196,7 +83189,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83228,7 +83221,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83301,7 +83294,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83404,7 +83397,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83509,7 +83502,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83616,7 +83609,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83723,7 +83716,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83832,7 +83825,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83937,7 +83930,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83966,10 +83959,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84040,7 +84033,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>
@@ -73478,7 +73478,7 @@
       </c>
       <c r="F649" s="2"/>
       <c r="G649" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H649" t="s" s="2">
         <v>84</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -822,10 +822,10 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
+  </si>
+  <si>
+    <t>Correspond à l’organisation responsable de la conservation, de la maintenance et/ou de l’accès au document, et non nécessairement à l’auteur ou à l’hébergeur technique.</t>
   </si>
   <si>
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -73793,7 +73793,7 @@
       </c>
       <c r="F652" s="2"/>
       <c r="G652" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H652" t="s" s="2">
         <v>84</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1321">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Commentaire associé au document.</t>
+    <t>Description du document source, lisible par l'homme, correspondant au commentaire associé au document</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>
@@ -3876,6 +3876,9 @@
   </si>
   <si>
     <t>Target of the relationship</t>
+  </si>
+  <si>
+    <t>Commentaire associé au document.</t>
   </si>
   <si>
     <t>Document contenu.</t>
@@ -5612,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="174">
@@ -5620,7 +5623,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="175">
@@ -5636,7 +5639,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="177">
@@ -5644,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="178">
@@ -5698,7 +5701,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="185">
@@ -5742,7 +5745,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="191">
@@ -74544,7 +74547,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>283</v>
+        <v>1239</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74758,7 +74761,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75697,7 +75700,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75804,7 +75807,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76230,7 +76233,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77233,7 +77236,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="685">
@@ -77338,7 +77341,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="686">
@@ -77551,7 +77554,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77654,7 +77657,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77759,7 +77762,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77862,7 +77865,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77965,7 +77968,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78070,7 +78073,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78175,7 +78178,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78280,7 +78283,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78385,7 +78388,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78490,7 +78493,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78595,7 +78598,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78700,7 +78703,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78805,7 +78808,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78910,7 +78913,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79015,7 +79018,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79047,7 +79050,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79120,7 +79123,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79134,7 +79137,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79221,7 +79224,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79255,7 +79258,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79321,18 +79324,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79429,13 +79432,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79532,13 +79535,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79578,7 +79581,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79637,13 +79640,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79703,7 +79706,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79738,16 +79741,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79769,13 +79772,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M709" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N709" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79843,16 +79846,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79874,13 +79877,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79948,10 +79951,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -79982,7 +79985,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80053,16 +80056,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80084,10 +80087,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80158,13 +80161,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80261,13 +80264,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80364,13 +80367,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80469,13 +80472,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80572,7 +80575,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80675,7 +80678,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80776,7 +80779,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80807,10 +80810,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80881,7 +80884,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80915,7 +80918,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -80986,7 +80989,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81018,7 +81021,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81091,7 +81094,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81123,7 +81126,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81198,7 +81201,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81230,7 +81233,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81303,7 +81306,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81335,7 +81338,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81354,7 +81357,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81408,7 +81411,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81515,7 +81518,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81618,7 +81621,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81650,7 +81653,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81725,7 +81728,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81754,10 +81757,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81832,13 +81835,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81935,13 +81938,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82040,16 +82043,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1297</v>
       </c>
-      <c r="C731" t="s" s="2">
-        <v>1296</v>
-      </c>
       <c r="D731" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82071,13 +82074,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82145,13 +82148,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82248,13 +82251,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82351,13 +82354,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82397,7 +82400,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82456,13 +82459,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82485,7 +82488,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82559,13 +82562,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82664,13 +82667,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82769,13 +82772,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82874,13 +82877,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82979,7 +82982,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83086,7 +83089,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83118,7 +83121,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83189,7 +83192,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83221,7 +83224,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83294,7 +83297,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83397,7 +83400,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83502,7 +83505,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83609,7 +83612,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83716,7 +83719,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83825,7 +83828,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83930,7 +83933,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83959,10 +83962,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84033,7 +84036,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1321">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -943,8 +943,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-bind-securityLabel:Les codes pour cet élément doivent provenir du ValueSet spécifié par le standard. Lorsqu’aucun code ne correspond au concept recherché, un code provenant de la terminologie de référence TRE_A07-StatusVisibiliteDocument, OID : 1.2.250.1.213.1.1.4.13 peut être utilisé. {null}</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J08-XdsConfidentialityCode-CISIS/FHIR/JDV-J08-XdsConfidentialityCode-CISIS</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -9859,11 +9858,9 @@
       <c r="Y39" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="Z39" s="2"/>
       <c r="AA39" t="s" s="2">
-        <v>143</v>
+        <v>292</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>75</v>
@@ -9893,7 +9890,7 @@
         <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>292</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40">
@@ -74690,11 +74687,9 @@
       <c r="Y660" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="Z660" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="Z660" s="2"/>
       <c r="AA660" t="s" s="2">
-        <v>143</v>
+        <v>292</v>
       </c>
       <c r="AB660" t="s" s="2">
         <v>75</v>
@@ -74724,7 +74719,7 @@
         <v>75</v>
       </c>
       <c r="AK660" t="s" s="2">
-        <v>292</v>
+        <v>96</v>
       </c>
     </row>
     <row r="661">

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3835,7 +3835,7 @@
     <t>PDSm Simplified Publish Document Reference</t>
   </si>
   <si>
-    <t>Profil utilisé dans le cadre du flux 9 d'ajout simplifié de document. Le flux et le profil sont inspirés d’IHE MHD, transaction ITI-105.
+    <t>Profil utilisé dans le cadre du flux 9 de publication simplifiée de document. Le flux et le profil sont inspirés d’IHE MHD, transaction ITI-105.
 Contrairement au profil PDSm_ComprehensiveDocumentReference, le document est directement inclus dans DocumentReference.attachment.data et non dans une ressource « Binary » externe.
 La publication simplifiée est une simple requête HTTP POST d'une ressource DocumentReference conforme à ce profil.</t>
   </si>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1324">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3865,16 +3865,28 @@
 </t>
   </si>
   <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
-  </si>
-  <si>
-    <t>replaces | transforms | signs | appends</t>
-  </si>
-  <si>
-    <t>Target of the relationship</t>
+    <t>Relation avec le document remplacé</t>
+  </si>
+  <si>
+    <t>Renseigné lorsque le flux envoyé correspond au remplacement d’un document existant.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-relatesTo-rempl:Renseigné lorsque le flux envoyé correspond au remplacement d’un document existant. {null}</t>
+  </si>
+  <si>
+    <t>Représente le type d’association entre deux documents.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-bind-relatesToCode:Doit valoir « replaces » lorsque le flux envoyé correspond au remplacement d’un document existant. {null}</t>
+  </si>
+  <si>
+    <t>Représente l’identifiant du document remplacé.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-bind-relatesToTarget:Référence contrainte au profil PDSm_SimplifiedPublish. {null}</t>
   </si>
   <si>
     <t>Commentaire associé au document.</t>
@@ -5614,7 +5626,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="174">
@@ -5622,7 +5634,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="175">
@@ -5638,7 +5650,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="177">
@@ -5646,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="178">
@@ -5700,7 +5712,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="185">
@@ -5744,7 +5756,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="191">
@@ -73984,7 +73996,7 @@
         <v>75</v>
       </c>
       <c r="AK653" t="s" s="2">
-        <v>96</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="654">
@@ -74336,7 +74348,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>273</v>
@@ -74404,7 +74416,7 @@
         <v>75</v>
       </c>
       <c r="AK657" t="s" s="2">
-        <v>96</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="658">
@@ -74441,7 +74453,7 @@
         <v>278</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>280</v>
@@ -74507,7 +74519,7 @@
         <v>75</v>
       </c>
       <c r="AK658" t="s" s="2">
-        <v>96</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="659">
@@ -74544,7 +74556,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74756,7 +74768,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75695,7 +75707,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75802,7 +75814,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76228,7 +76240,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77231,7 +77243,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="685">
@@ -77336,7 +77348,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="686">
@@ -77549,7 +77561,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77652,7 +77664,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77757,7 +77769,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77860,7 +77872,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77963,7 +77975,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78068,7 +78080,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78173,7 +78185,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78278,7 +78290,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78383,7 +78395,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78488,7 +78500,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78593,7 +78605,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78698,7 +78710,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78803,7 +78815,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78908,7 +78920,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79013,7 +79025,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79045,7 +79057,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79118,7 +79130,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79132,7 +79144,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79219,7 +79231,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79253,7 +79265,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79319,18 +79331,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1254</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79427,13 +79439,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79530,13 +79542,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79576,7 +79588,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79635,13 +79647,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79701,7 +79713,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79736,16 +79748,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79767,13 +79779,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="M709" t="s" s="2">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="N709" t="s" s="2">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79841,16 +79853,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79872,13 +79884,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79946,10 +79958,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -79980,7 +79992,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80051,16 +80063,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80082,10 +80094,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80156,13 +80168,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80259,13 +80271,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80362,13 +80374,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80467,13 +80479,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80570,7 +80582,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80673,7 +80685,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80774,7 +80786,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80805,10 +80817,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80879,7 +80891,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80913,7 +80925,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -80984,7 +80996,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81016,7 +81028,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81089,7 +81101,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81121,7 +81133,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81196,7 +81208,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81228,7 +81240,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81301,7 +81313,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81333,7 +81345,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81352,7 +81364,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81406,7 +81418,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81513,7 +81525,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81616,7 +81628,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81648,7 +81660,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81723,7 +81735,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81752,10 +81764,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81830,13 +81842,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81933,13 +81945,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82038,16 +82050,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D731" t="s" s="2">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82069,13 +82081,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82143,13 +82155,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82246,13 +82258,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82349,13 +82361,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82395,7 +82407,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82454,13 +82466,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82483,7 +82495,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82557,13 +82569,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82662,13 +82674,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82767,13 +82779,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82872,13 +82884,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82977,7 +82989,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83084,7 +83096,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83116,7 +83128,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83187,7 +83199,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83219,7 +83231,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83292,7 +83304,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83395,7 +83407,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83500,7 +83512,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83607,7 +83619,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83714,7 +83726,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83823,7 +83835,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83928,7 +83940,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83957,10 +83969,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84031,7 +84043,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
